--- a/outputs/analysis/analysis_output/tables/part2/salary_table_completeness_by_year.xlsx
+++ b/outputs/analysis/analysis_output/tables/part2/salary_table_completeness_by_year.xlsx
@@ -566,13 +566,13 @@
         <v>2008</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -580,13 +580,13 @@
         <v>2009</v>
       </c>
       <c r="B3" t="n">
-        <v>83.33333333333334</v>
+        <v>86.36363636363636</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -594,13 +594,13 @@
         <v>2010</v>
       </c>
       <c r="B4" t="n">
-        <v>76.92307692307693</v>
+        <v>93.18181818181817</v>
       </c>
       <c r="C4" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -608,13 +608,13 @@
         <v>2011</v>
       </c>
       <c r="B5" t="n">
-        <v>75</v>
+        <v>90.69767441860465</v>
       </c>
       <c r="C5" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6">
@@ -622,13 +622,13 @@
         <v>2012</v>
       </c>
       <c r="B6" t="n">
-        <v>72.09302325581395</v>
+        <v>97.59036144578313</v>
       </c>
       <c r="C6" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D6" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7">
@@ -636,13 +636,13 @@
         <v>2013</v>
       </c>
       <c r="B7" t="n">
-        <v>65.07936507936508</v>
+        <v>86.88524590163934</v>
       </c>
       <c r="C7" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D7" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
@@ -650,13 +650,13 @@
         <v>2014</v>
       </c>
       <c r="B8" t="n">
-        <v>67.9245283018868</v>
+        <v>82.17821782178217</v>
       </c>
       <c r="C8" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D8" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
@@ -664,13 +664,13 @@
         <v>2015</v>
       </c>
       <c r="B9" t="n">
-        <v>69.3069306930693</v>
+        <v>87.62886597938144</v>
       </c>
       <c r="C9" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D9" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -678,13 +678,13 @@
         <v>2016</v>
       </c>
       <c r="B10" t="n">
-        <v>80.85106382978722</v>
+        <v>95.55555555555556</v>
       </c>
       <c r="C10" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
@@ -692,13 +692,13 @@
         <v>2017</v>
       </c>
       <c r="B11" t="n">
-        <v>80.83333333333333</v>
+        <v>93.85964912280701</v>
       </c>
       <c r="C11" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -706,13 +706,13 @@
         <v>2018</v>
       </c>
       <c r="B12" t="n">
-        <v>71.42857142857143</v>
+        <v>88.63636363636364</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">
@@ -720,13 +720,13 @@
         <v>2019</v>
       </c>
       <c r="B13" t="n">
-        <v>80.48780487804879</v>
+        <v>89.56521739130436</v>
       </c>
       <c r="C13" t="n">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -734,13 +734,13 @@
         <v>2020</v>
       </c>
       <c r="B14" t="n">
-        <v>76.74418604651163</v>
+        <v>100</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -748,13 +748,13 @@
         <v>2021</v>
       </c>
       <c r="B15" t="n">
-        <v>84.93150684931507</v>
+        <v>92.64705882352942</v>
       </c>
       <c r="C15" t="n">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D15" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16">
@@ -762,13 +762,13 @@
         <v>2022</v>
       </c>
       <c r="B16" t="n">
-        <v>66.32653061224489</v>
+        <v>93.47826086956522</v>
       </c>
       <c r="C16" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17">
@@ -776,13 +776,13 @@
         <v>2023</v>
       </c>
       <c r="B17" t="n">
-        <v>76.92307692307693</v>
+        <v>96.96969696969697</v>
       </c>
       <c r="C17" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18">
@@ -790,13 +790,13 @@
         <v>2024</v>
       </c>
       <c r="B18" t="n">
-        <v>79.86111111111111</v>
+        <v>96.99248120300751</v>
       </c>
       <c r="C18" t="n">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D18" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19">
